--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R39aa6efd19d14597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R672622f569514852"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R672622f569514852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3752fff64c2a468a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3752fff64c2a468a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82236142c790448e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82236142c790448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc331a30b7069462f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc331a30b7069462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R91c8367bb43e4f97"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R91c8367bb43e4f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R321bc80f68f24166"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R321bc80f68f24166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5f8bd4231434be4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5f8bd4231434be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra8375c77e7a34150"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra8375c77e7a34150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R855dcc86bc594988"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R855dcc86bc594988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfef8dbe429f349fd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfef8dbe429f349fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bd0d3d22e0240ab"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bd0d3d22e0240ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcce1d5d541cc4eb7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcce1d5d541cc4eb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R708d7cae19ef44d0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R708d7cae19ef44d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8acb057a4eaa4580"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8acb057a4eaa4580"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R069b762ebe43476e"/>
   </x:sheets>
 </x:workbook>
 </file>
